--- a/day.xlsx
+++ b/day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>day</t>
   </si>
   <si>
     <t>profit</t>
+  </si>
+  <si>
+    <t>probRarity1</t>
+  </si>
+  <si>
+    <t>probRarity2</t>
+  </si>
+  <si>
+    <t>probRarity3</t>
   </si>
 </sst>
 </file>
@@ -965,167 +974,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2">
+        <v>0.8</v>
+      </c>
+      <c r="D2">
+        <v>0.2</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>0.8</v>
+      </c>
+      <c r="D3">
+        <v>0.2</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>0.8</v>
+      </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>160</v>
+      </c>
+      <c r="C5">
+        <v>0.6</v>
+      </c>
+      <c r="D5">
+        <v>0.4</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>160</v>
+      </c>
+      <c r="C6">
+        <v>0.6</v>
+      </c>
+      <c r="D6">
+        <v>0.4</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>160</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>160</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>160</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+      <c r="D9">
+        <v>0.5</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C10">
+        <v>0.4</v>
+      </c>
+      <c r="D10">
+        <v>0.4</v>
+      </c>
+      <c r="E10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C11">
+        <v>0.4</v>
+      </c>
+      <c r="D11">
+        <v>0.4</v>
+      </c>
+      <c r="E11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C12">
+        <v>0.4</v>
+      </c>
+      <c r="D12">
+        <v>0.4</v>
+      </c>
+      <c r="E12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C13">
+        <v>0.4</v>
+      </c>
+      <c r="D13">
+        <v>0.4</v>
+      </c>
+      <c r="E13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C14">
+        <v>0.4</v>
+      </c>
+      <c r="D14">
+        <v>0.4</v>
+      </c>
+      <c r="E14">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C15">
+        <v>0.4</v>
+      </c>
+      <c r="D15">
+        <v>0.4</v>
+      </c>
+      <c r="E15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C16">
+        <v>0.4</v>
+      </c>
+      <c r="D16">
+        <v>0.4</v>
+      </c>
+      <c r="E16">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C17">
+        <v>0.4</v>
+      </c>
+      <c r="D17">
+        <v>0.4</v>
+      </c>
+      <c r="E17">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C18">
+        <v>0.4</v>
+      </c>
+      <c r="D18">
+        <v>0.4</v>
+      </c>
+      <c r="E18">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>300</v>
+      </c>
+      <c r="C19">
+        <v>0.4</v>
+      </c>
+      <c r="D19">
+        <v>0.4</v>
+      </c>
+      <c r="E19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>300</v>
+      </c>
+      <c r="C20">
+        <v>0.4</v>
+      </c>
+      <c r="D20">
+        <v>0.4</v>
+      </c>
+      <c r="E20">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>day</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>probRarity3</t>
+  </si>
+  <si>
+    <t>drawNum</t>
+  </si>
+  <si>
+    <t>getCardNum</t>
   </si>
 </sst>
 </file>
@@ -974,15 +980,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -998,8 +1004,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1015,8 +1027,14 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1032,8 +1050,14 @@
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1049,8 +1073,14 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1066,8 +1096,14 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1083,8 +1119,14 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1100,8 +1142,14 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1117,8 +1165,14 @@
       <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1134,8 +1188,14 @@
       <c r="E9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1151,8 +1211,14 @@
       <c r="E10">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1168,8 +1234,14 @@
       <c r="E11">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1185,8 +1257,14 @@
       <c r="E12">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1202,8 +1280,14 @@
       <c r="E13">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1219,8 +1303,14 @@
       <c r="E14">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1236,8 +1326,14 @@
       <c r="E15">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1253,8 +1349,14 @@
       <c r="E16">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1270,8 +1372,14 @@
       <c r="E17">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1287,8 +1395,14 @@
       <c r="E18">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1304,8 +1418,14 @@
       <c r="E19">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1320,6 +1440,12 @@
       </c>
       <c r="E20">
         <v>0.2</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>day</t>
   </si>
@@ -50,6 +50,60 @@
   </si>
   <si>
     <t>getCardNum</t>
+  </si>
+  <si>
+    <t>dailyDialog</t>
+  </si>
+  <si>
+    <t>specialDialog</t>
+  </si>
+  <si>
+    <t>target1</t>
+  </si>
+  <si>
+    <t>target2</t>
+  </si>
+  <si>
+    <t>target3</t>
+  </si>
+  <si>
+    <t>target4</t>
+  </si>
+  <si>
+    <t>normalEnd1_1</t>
+  </si>
+  <si>
+    <t>normalEnd1_2</t>
+  </si>
+  <si>
+    <t>special1_1</t>
+  </si>
+  <si>
+    <t>normalEnd1_3</t>
+  </si>
+  <si>
+    <t>normalEnd1_4</t>
+  </si>
+  <si>
+    <t>special1_2</t>
+  </si>
+  <si>
+    <t>normalEnd1_5</t>
+  </si>
+  <si>
+    <t>normalEnd1_6</t>
+  </si>
+  <si>
+    <t>special1_3</t>
+  </si>
+  <si>
+    <t>normalEnd1_7</t>
+  </si>
+  <si>
+    <t>normalEnd1_8</t>
+  </si>
+  <si>
+    <t>special1_4</t>
   </si>
 </sst>
 </file>
@@ -980,15 +1034,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:M20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="8" max="8" width="14.8181818181818" customWidth="1"/>
+    <col min="9" max="9" width="14.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1010,8 +1066,26 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1033,8 +1107,11 @@
       <c r="G2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1056,8 +1133,11 @@
       <c r="G3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1079,8 +1159,11 @@
       <c r="G4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1102,8 +1185,11 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1125,8 +1211,11 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1148,8 +1237,11 @@
       <c r="G7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1171,8 +1263,11 @@
       <c r="G8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1194,8 +1289,11 @@
       <c r="G9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1217,8 +1315,11 @@
       <c r="G10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1240,8 +1341,11 @@
       <c r="G11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1263,8 +1367,11 @@
       <c r="G12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1286,8 +1393,11 @@
       <c r="G13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1310,7 +1420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1333,7 +1443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>15</v>
       </c>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>day</t>
   </si>
@@ -76,34 +76,52 @@
     <t>normalEnd1_2</t>
   </si>
   <si>
+    <t>simpleEnd1_1</t>
+  </si>
+  <si>
     <t>special1_1</t>
   </si>
   <si>
+    <t>simpleEnd1_2</t>
+  </si>
+  <si>
     <t>normalEnd1_3</t>
   </si>
   <si>
+    <t>simpleEnd1_4</t>
+  </si>
+  <si>
+    <t>special1_2</t>
+  </si>
+  <si>
     <t>normalEnd1_4</t>
   </si>
   <si>
-    <t>special1_2</t>
-  </si>
-  <si>
     <t>normalEnd1_5</t>
   </si>
   <si>
+    <t>simpleEnd1_5</t>
+  </si>
+  <si>
+    <t>special1_3</t>
+  </si>
+  <si>
     <t>normalEnd1_6</t>
   </si>
   <si>
-    <t>special1_3</t>
-  </si>
-  <si>
     <t>normalEnd1_7</t>
   </si>
   <si>
-    <t>normalEnd1_8</t>
+    <t>simpleEnd1_8</t>
   </si>
   <si>
     <t>special1_4</t>
+  </si>
+  <si>
+    <t>simpleEnd1_3</t>
+  </si>
+  <si>
+    <t>simpleEnd1_6</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
@@ -1159,8 +1177,11 @@
       <c r="G4">
         <v>2</v>
       </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1186,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1212,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1237,8 +1258,11 @@
       <c r="G7">
         <v>1</v>
       </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1264,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1290,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1315,8 +1339,11 @@
       <c r="G10">
         <v>1</v>
       </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1342,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1368,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1393,8 +1420,11 @@
       <c r="G13">
         <v>1</v>
       </c>
+      <c r="H13" t="s">
+        <v>27</v>
+      </c>
       <c r="I13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1419,6 +1449,9 @@
       <c r="G14">
         <v>1</v>
       </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15">
@@ -1442,6 +1475,9 @@
       <c r="G15">
         <v>1</v>
       </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16">
@@ -1465,8 +1501,11 @@
       <c r="G16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1488,8 +1527,11 @@
       <c r="G17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1511,51 +1553,8 @@
       <c r="G18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>300</v>
-      </c>
-      <c r="C19">
-        <v>0.4</v>
-      </c>
-      <c r="D19">
-        <v>0.4</v>
-      </c>
-      <c r="E19">
-        <v>0.2</v>
-      </c>
-      <c r="F19">
-        <v>4</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>300</v>
-      </c>
-      <c r="C20">
-        <v>0.4</v>
-      </c>
-      <c r="D20">
-        <v>0.4</v>
-      </c>
-      <c r="E20">
-        <v>0.2</v>
-      </c>
-      <c r="F20">
-        <v>4</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
+      <c r="H18" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>day</t>
   </si>
@@ -37,6 +37,9 @@
     <t>profit</t>
   </si>
   <si>
+    <t>workDialog</t>
+  </si>
+  <si>
     <t>probRarity1</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>target4</t>
   </si>
   <si>
+    <t>doWork1_1</t>
+  </si>
+  <si>
     <t>normalEnd1_1</t>
   </si>
   <si>
@@ -82,6 +88,9 @@
     <t>special1_1</t>
   </si>
   <si>
+    <t>doWork1_2</t>
+  </si>
+  <si>
     <t>simpleEnd1_2</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t>special1_2</t>
   </si>
   <si>
+    <t>doWork1_3</t>
+  </si>
+  <si>
     <t>normalEnd1_4</t>
   </si>
   <si>
@@ -104,6 +116,9 @@
   </si>
   <si>
     <t>special1_3</t>
+  </si>
+  <si>
+    <t>doWork1_4</t>
   </si>
   <si>
     <t>normalEnd1_6</t>
@@ -1052,17 +1067,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="8" max="8" width="14.8181818181818" customWidth="1"/>
-    <col min="9" max="9" width="14.4545454545455" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="16.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="9" max="9" width="14.8181818181818" customWidth="1"/>
+    <col min="10" max="10" width="14.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1102,459 +1117,513 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2">
         <v>0.8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.2</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
       <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
         <v>0.8</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.2</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
       <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
         <v>0.8</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.2</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
       <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
       <c r="I4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>160</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
         <v>0.6</v>
       </c>
-      <c r="D5">
-        <v>0.4</v>
-      </c>
       <c r="E5">
+        <v>0.4</v>
+      </c>
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
       <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>160</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
         <v>0.6</v>
       </c>
-      <c r="D6">
-        <v>0.4</v>
-      </c>
       <c r="E6">
+        <v>0.4</v>
+      </c>
+      <c r="F6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
       <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>160</v>
       </c>
-      <c r="C7">
-        <v>0.5</v>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
         <v>0.5</v>
       </c>
       <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
       <c r="I7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>160</v>
       </c>
-      <c r="C8">
-        <v>0.5</v>
+      <c r="C8" t="s">
+        <v>24</v>
       </c>
       <c r="D8">
         <v>0.5</v>
       </c>
       <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
       <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>160</v>
       </c>
-      <c r="C9">
-        <v>0.5</v>
+      <c r="C9" t="s">
+        <v>24</v>
       </c>
       <c r="D9">
         <v>0.5</v>
       </c>
       <c r="E9">
+        <v>0.5</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
       <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>300</v>
       </c>
-      <c r="C10">
-        <v>0.4</v>
+      <c r="C10" t="s">
+        <v>24</v>
       </c>
       <c r="D10">
         <v>0.4</v>
       </c>
       <c r="E10">
+        <v>0.4</v>
+      </c>
+      <c r="F10">
         <v>0.2</v>
       </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
       <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
       <c r="I10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>300</v>
       </c>
-      <c r="C11">
-        <v>0.4</v>
+      <c r="C11" t="s">
+        <v>29</v>
       </c>
       <c r="D11">
         <v>0.4</v>
       </c>
       <c r="E11">
+        <v>0.4</v>
+      </c>
+      <c r="F11">
         <v>0.2</v>
       </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
       <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>300</v>
       </c>
-      <c r="C12">
-        <v>0.4</v>
+      <c r="C12" t="s">
+        <v>29</v>
       </c>
       <c r="D12">
         <v>0.4</v>
       </c>
       <c r="E12">
+        <v>0.4</v>
+      </c>
+      <c r="F12">
         <v>0.2</v>
       </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
       <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
         <v>1</v>
       </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>300</v>
       </c>
-      <c r="C13">
-        <v>0.4</v>
+      <c r="C13" t="s">
+        <v>29</v>
       </c>
       <c r="D13">
         <v>0.4</v>
       </c>
       <c r="E13">
+        <v>0.4</v>
+      </c>
+      <c r="F13">
         <v>0.2</v>
       </c>
-      <c r="F13">
-        <v>4</v>
-      </c>
       <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
       <c r="I13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>300</v>
       </c>
-      <c r="C14">
-        <v>0.4</v>
+      <c r="C14" t="s">
+        <v>29</v>
       </c>
       <c r="D14">
         <v>0.4</v>
       </c>
       <c r="E14">
+        <v>0.4</v>
+      </c>
+      <c r="F14">
         <v>0.2</v>
       </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
       <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
         <v>1</v>
       </c>
-      <c r="H14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>300</v>
       </c>
-      <c r="C15">
-        <v>0.4</v>
+      <c r="C15" t="s">
+        <v>29</v>
       </c>
       <c r="D15">
         <v>0.4</v>
       </c>
       <c r="E15">
+        <v>0.4</v>
+      </c>
+      <c r="F15">
         <v>0.2</v>
       </c>
-      <c r="F15">
-        <v>4</v>
-      </c>
       <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
         <v>1</v>
       </c>
-      <c r="H15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="I15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>300</v>
       </c>
-      <c r="C16">
-        <v>0.4</v>
+      <c r="C16" t="s">
+        <v>29</v>
       </c>
       <c r="D16">
         <v>0.4</v>
       </c>
       <c r="E16">
+        <v>0.4</v>
+      </c>
+      <c r="F16">
         <v>0.2</v>
       </c>
-      <c r="F16">
-        <v>4</v>
-      </c>
       <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
         <v>1</v>
       </c>
-      <c r="H16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>300</v>
       </c>
-      <c r="C17">
-        <v>0.4</v>
+      <c r="C17" t="s">
+        <v>29</v>
       </c>
       <c r="D17">
         <v>0.4</v>
       </c>
       <c r="E17">
+        <v>0.4</v>
+      </c>
+      <c r="F17">
         <v>0.2</v>
       </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
       <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
         <v>1</v>
       </c>
-      <c r="H17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>300</v>
       </c>
-      <c r="C18">
-        <v>0.4</v>
+      <c r="C18" t="s">
+        <v>29</v>
       </c>
       <c r="D18">
         <v>0.4</v>
       </c>
       <c r="E18">
+        <v>0.4</v>
+      </c>
+      <c r="F18">
         <v>0.2</v>
       </c>
-      <c r="F18">
-        <v>4</v>
-      </c>
       <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
         <v>1</v>
       </c>
-      <c r="H18" t="s">
-        <v>30</v>
+      <c r="I18" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>day</t>
   </si>
@@ -79,52 +79,76 @@
     <t>normalEnd1_1</t>
   </si>
   <si>
+    <t>doWork1_2</t>
+  </si>
+  <si>
     <t>normalEnd1_2</t>
   </si>
   <si>
+    <t>doWork1_3</t>
+  </si>
+  <si>
     <t>simpleEnd1_1</t>
   </si>
   <si>
     <t>special1_1</t>
   </si>
   <si>
-    <t>doWork1_2</t>
+    <t>doWork1_4</t>
   </si>
   <si>
     <t>simpleEnd1_2</t>
   </si>
   <si>
+    <t>doWork2_1</t>
+  </si>
+  <si>
     <t>normalEnd1_3</t>
   </si>
   <si>
+    <t>doWork2_2</t>
+  </si>
+  <si>
     <t>simpleEnd1_4</t>
   </si>
   <si>
     <t>special1_2</t>
   </si>
   <si>
-    <t>doWork1_3</t>
+    <t>doWork2_3</t>
   </si>
   <si>
     <t>normalEnd1_4</t>
   </si>
   <si>
+    <t>doWork2_4</t>
+  </si>
+  <si>
     <t>normalEnd1_5</t>
   </si>
   <si>
+    <t>doWork3_1</t>
+  </si>
+  <si>
     <t>simpleEnd1_5</t>
   </si>
   <si>
     <t>special1_3</t>
   </si>
   <si>
-    <t>doWork1_4</t>
+    <t>doWork3_2</t>
   </si>
   <si>
     <t>normalEnd1_6</t>
   </si>
   <si>
+    <t>doWork3_3</t>
+  </si>
+  <si>
     <t>normalEnd1_7</t>
+  </si>
+  <si>
+    <t>doWork3_4</t>
   </si>
   <si>
     <t>simpleEnd1_8</t>
@@ -1158,7 +1182,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>0.8</v>
@@ -1176,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1187,7 +1211,7 @@
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>0.8</v>
@@ -1205,10 +1229,10 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1219,7 +1243,7 @@
         <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>0.6</v>
@@ -1237,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1248,7 +1272,7 @@
         <v>160</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1266,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1277,7 +1301,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>0.5</v>
@@ -1295,10 +1319,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1309,7 +1333,7 @@
         <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>0.5</v>
@@ -1327,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1338,7 +1362,7 @@
         <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>0.5</v>
@@ -1356,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1367,7 +1391,7 @@
         <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>0.4</v>
@@ -1385,10 +1409,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1399,7 +1423,7 @@
         <v>300</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D11">
         <v>0.4</v>
@@ -1417,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1428,7 +1452,7 @@
         <v>300</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D12">
         <v>0.4</v>
@@ -1446,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1457,7 +1481,7 @@
         <v>300</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D13">
         <v>0.4</v>
@@ -1475,10 +1499,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1489,7 +1513,7 @@
         <v>300</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>0.4</v>
@@ -1507,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1518,7 +1542,7 @@
         <v>300</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>0.4</v>
@@ -1536,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1547,7 +1571,7 @@
         <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>0.4</v>
@@ -1565,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1576,7 +1600,7 @@
         <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>0.4</v>
@@ -1594,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1605,7 +1629,7 @@
         <v>300</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D18">
         <v>0.4</v>
@@ -1623,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -76,7 +76,7 @@
     <t>doWork1_1</t>
   </si>
   <si>
-    <t>normalEnd1_1</t>
+    <t>cardFirstEnd</t>
   </si>
   <si>
     <t>doWork1_2</t>

--- a/day.xlsx
+++ b/day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>day</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
     <t>profit</t>
   </si>
   <si>
@@ -61,6 +64,9 @@
     <t>specialDialog</t>
   </si>
   <si>
+    <t>failedDialog</t>
+  </si>
+  <si>
     <t>target1</t>
   </si>
   <si>
@@ -73,18 +79,27 @@
     <t>target4</t>
   </si>
   <si>
+    <t>05_16</t>
+  </si>
+  <si>
     <t>doWork1_1</t>
   </si>
   <si>
     <t>cardFirstEnd</t>
   </si>
   <si>
+    <t>05_17</t>
+  </si>
+  <si>
     <t>doWork1_2</t>
   </si>
   <si>
     <t>normalEnd1_2</t>
   </si>
   <si>
+    <t>05_18</t>
+  </si>
+  <si>
     <t>doWork1_3</t>
   </si>
   <si>
@@ -94,18 +109,30 @@
     <t>special1_1</t>
   </si>
   <si>
+    <t>05_19</t>
+  </si>
+  <si>
     <t>doWork1_4</t>
   </si>
   <si>
     <t>simpleEnd1_2</t>
   </si>
   <si>
+    <t>failed1_1</t>
+  </si>
+  <si>
+    <t>05_20</t>
+  </si>
+  <si>
     <t>doWork2_1</t>
   </si>
   <si>
     <t>normalEnd1_3</t>
   </si>
   <si>
+    <t>05_21</t>
+  </si>
+  <si>
     <t>doWork2_2</t>
   </si>
   <si>
@@ -115,18 +142,30 @@
     <t>special1_2</t>
   </si>
   <si>
+    <t>05_22</t>
+  </si>
+  <si>
     <t>doWork2_3</t>
   </si>
   <si>
     <t>normalEnd1_4</t>
   </si>
   <si>
+    <t>failed1_2</t>
+  </si>
+  <si>
+    <t>05_23</t>
+  </si>
+  <si>
     <t>doWork2_4</t>
   </si>
   <si>
     <t>normalEnd1_5</t>
   </si>
   <si>
+    <t>05_24</t>
+  </si>
+  <si>
     <t>doWork3_1</t>
   </si>
   <si>
@@ -136,18 +175,30 @@
     <t>special1_3</t>
   </si>
   <si>
+    <t>05_25</t>
+  </si>
+  <si>
     <t>doWork3_2</t>
   </si>
   <si>
     <t>normalEnd1_6</t>
   </si>
   <si>
+    <t>05_26</t>
+  </si>
+  <si>
     <t>doWork3_3</t>
   </si>
   <si>
     <t>normalEnd1_7</t>
   </si>
   <si>
+    <t>failed1_3</t>
+  </si>
+  <si>
+    <t>05_27</t>
+  </si>
+  <si>
     <t>doWork3_4</t>
   </si>
   <si>
@@ -157,7 +208,25 @@
     <t>special1_4</t>
   </si>
   <si>
+    <t>05_28</t>
+  </si>
+  <si>
+    <t>05_29</t>
+  </si>
+  <si>
     <t>simpleEnd1_3</t>
+  </si>
+  <si>
+    <t>05_30</t>
+  </si>
+  <si>
+    <t>failed1_4</t>
+  </si>
+  <si>
+    <t>05_31</t>
+  </si>
+  <si>
+    <t>06_01</t>
   </si>
   <si>
     <t>simpleEnd1_6</t>
@@ -1091,17 +1160,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="16.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="9" max="9" width="14.8181818181818" customWidth="1"/>
-    <col min="10" max="10" width="14.4545454545455" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="16.2727272727273" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="10" max="10" width="14.8181818181818" customWidth="1"/>
+    <col min="11" max="11" width="14.4545454545455" customWidth="1"/>
+    <col min="12" max="12" width="14.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1144,510 +1214,579 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
         <v>100</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2">
         <v>0.8</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.2</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
       <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
+      <c r="J2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
         <v>100</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3">
         <v>0.8</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.2</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>4</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
-        <v>17</v>
+      <c r="J3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
         <v>0.8</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.2</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
         <v>160</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5">
         <v>0.6</v>
       </c>
-      <c r="E5">
-        <v>0.4</v>
-      </c>
       <c r="F5">
+        <v>0.4</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>4</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
-        <v>22</v>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6">
         <v>160</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6">
         <v>0.6</v>
       </c>
-      <c r="E6">
-        <v>0.4</v>
-      </c>
       <c r="F6">
+        <v>0.4</v>
+      </c>
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="I6" t="s">
-        <v>24</v>
+      <c r="J6" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
         <v>160</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>0.5</v>
+      <c r="D7" t="s">
+        <v>34</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>1</v>
       </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8">
         <v>160</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>0.5</v>
+      <c r="D8" t="s">
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>4</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="I8" t="s">
-        <v>29</v>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
         <v>160</v>
       </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
+      <c r="D9" t="s">
+        <v>42</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
+        <v>0.5</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>1</v>
       </c>
-      <c r="I9" t="s">
-        <v>31</v>
+      <c r="J9" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10">
         <v>300</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>0.4</v>
+      <c r="D10" t="s">
+        <v>45</v>
       </c>
       <c r="E10">
         <v>0.4</v>
       </c>
       <c r="F10">
+        <v>0.4</v>
+      </c>
+      <c r="G10">
         <v>0.2</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>4</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="I10" t="s">
-        <v>33</v>
-      </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>46</v>
+      </c>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11">
         <v>300</v>
       </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11">
-        <v>0.4</v>
+      <c r="D11" t="s">
+        <v>49</v>
       </c>
       <c r="E11">
         <v>0.4</v>
       </c>
       <c r="F11">
+        <v>0.4</v>
+      </c>
+      <c r="G11">
         <v>0.2</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>4</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1</v>
       </c>
-      <c r="I11" t="s">
-        <v>36</v>
+      <c r="J11" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12">
         <v>300</v>
       </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12">
-        <v>0.4</v>
+      <c r="D12" t="s">
+        <v>52</v>
       </c>
       <c r="E12">
         <v>0.4</v>
       </c>
       <c r="F12">
+        <v>0.4</v>
+      </c>
+      <c r="G12">
         <v>0.2</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>4</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>1</v>
       </c>
-      <c r="I12" t="s">
-        <v>38</v>
+      <c r="J12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13">
         <v>300</v>
       </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13">
-        <v>0.4</v>
+      <c r="D13" t="s">
+        <v>56</v>
       </c>
       <c r="E13">
         <v>0.4</v>
       </c>
       <c r="F13">
+        <v>0.4</v>
+      </c>
+      <c r="G13">
         <v>0.2</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>4</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1</v>
       </c>
-      <c r="I13" t="s">
-        <v>40</v>
-      </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14">
         <v>300</v>
       </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14">
-        <v>0.4</v>
+      <c r="D14" t="s">
+        <v>20</v>
       </c>
       <c r="E14">
         <v>0.4</v>
       </c>
       <c r="F14">
+        <v>0.4</v>
+      </c>
+      <c r="G14">
         <v>0.2</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>4</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="I14" t="s">
-        <v>22</v>
+      <c r="J14" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15">
         <v>300</v>
       </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15">
-        <v>0.4</v>
+      <c r="D15" t="s">
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0.4</v>
       </c>
       <c r="F15">
+        <v>0.4</v>
+      </c>
+      <c r="G15">
         <v>0.2</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>4</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>1</v>
       </c>
-      <c r="I15" t="s">
-        <v>42</v>
+      <c r="J15" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16">
         <v>300</v>
       </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16">
-        <v>0.4</v>
+      <c r="D16" t="s">
+        <v>20</v>
       </c>
       <c r="E16">
         <v>0.4</v>
       </c>
       <c r="F16">
+        <v>0.4</v>
+      </c>
+      <c r="G16">
         <v>0.2</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>4</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1</v>
       </c>
-      <c r="I16" t="s">
-        <v>26</v>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
         <v>300</v>
       </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17">
-        <v>0.4</v>
+      <c r="D17" t="s">
+        <v>20</v>
       </c>
       <c r="E17">
         <v>0.4</v>
       </c>
       <c r="F17">
+        <v>0.4</v>
+      </c>
+      <c r="G17">
         <v>0.2</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>4</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>1</v>
       </c>
-      <c r="I17" t="s">
-        <v>33</v>
+      <c r="J17" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18">
         <v>300</v>
       </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18">
-        <v>0.4</v>
+      <c r="D18" t="s">
+        <v>20</v>
       </c>
       <c r="E18">
         <v>0.4</v>
       </c>
       <c r="F18">
+        <v>0.4</v>
+      </c>
+      <c r="G18">
         <v>0.2</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>4</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>1</v>
       </c>
-      <c r="I18" t="s">
-        <v>43</v>
+      <c r="J18" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11430"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1252,6 +1252,18 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
+      <c r="M2">
+        <v>1000</v>
+      </c>
+      <c r="N2">
+        <v>1000</v>
+      </c>
+      <c r="O2">
+        <v>1000</v>
+      </c>
+      <c r="P2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
@@ -1284,6 +1296,18 @@
       <c r="J3" t="s">
         <v>21</v>
       </c>
+      <c r="M3">
+        <v>1000</v>
+      </c>
+      <c r="N3">
+        <v>1000</v>
+      </c>
+      <c r="O3">
+        <v>1000</v>
+      </c>
+      <c r="P3">
+        <v>1000</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
@@ -1319,6 +1343,18 @@
       <c r="K4" t="s">
         <v>25</v>
       </c>
+      <c r="M4">
+        <v>1000</v>
+      </c>
+      <c r="N4">
+        <v>1000</v>
+      </c>
+      <c r="O4">
+        <v>1000</v>
+      </c>
+      <c r="P4">
+        <v>1000</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
@@ -1354,6 +1390,18 @@
       <c r="L5" t="s">
         <v>29</v>
       </c>
+      <c r="M5">
+        <v>1000</v>
+      </c>
+      <c r="N5">
+        <v>1000</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="P5">
+        <v>1000</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -1386,6 +1434,18 @@
       <c r="J6" t="s">
         <v>32</v>
       </c>
+      <c r="M6">
+        <v>1000</v>
+      </c>
+      <c r="N6">
+        <v>1000</v>
+      </c>
+      <c r="O6">
+        <v>1000</v>
+      </c>
+      <c r="P6">
+        <v>1000</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -1421,6 +1481,18 @@
       <c r="K7" t="s">
         <v>36</v>
       </c>
+      <c r="M7">
+        <v>1000</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+      <c r="O7">
+        <v>1000</v>
+      </c>
+      <c r="P7">
+        <v>1000</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -1456,6 +1528,18 @@
       <c r="L8" t="s">
         <v>40</v>
       </c>
+      <c r="M8">
+        <v>1000</v>
+      </c>
+      <c r="N8">
+        <v>1000</v>
+      </c>
+      <c r="O8">
+        <v>1000</v>
+      </c>
+      <c r="P8">
+        <v>1000</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -1488,6 +1572,18 @@
       <c r="J9" t="s">
         <v>43</v>
       </c>
+      <c r="M9">
+        <v>1000</v>
+      </c>
+      <c r="N9">
+        <v>1000</v>
+      </c>
+      <c r="O9">
+        <v>1000</v>
+      </c>
+      <c r="P9">
+        <v>1000</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
@@ -1523,6 +1619,18 @@
       <c r="K10" t="s">
         <v>47</v>
       </c>
+      <c r="M10">
+        <v>1000</v>
+      </c>
+      <c r="N10">
+        <v>1000</v>
+      </c>
+      <c r="O10">
+        <v>1000</v>
+      </c>
+      <c r="P10">
+        <v>1000</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
@@ -1555,6 +1663,18 @@
       <c r="J11" t="s">
         <v>50</v>
       </c>
+      <c r="M11">
+        <v>1000</v>
+      </c>
+      <c r="N11">
+        <v>1000</v>
+      </c>
+      <c r="O11">
+        <v>1000</v>
+      </c>
+      <c r="P11">
+        <v>1000</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
@@ -1590,6 +1710,18 @@
       <c r="L12" t="s">
         <v>54</v>
       </c>
+      <c r="M12">
+        <v>1000</v>
+      </c>
+      <c r="N12">
+        <v>1000</v>
+      </c>
+      <c r="O12">
+        <v>1000</v>
+      </c>
+      <c r="P12">
+        <v>1000</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -1625,6 +1757,18 @@
       <c r="K13" t="s">
         <v>58</v>
       </c>
+      <c r="M13">
+        <v>1000</v>
+      </c>
+      <c r="N13">
+        <v>1000</v>
+      </c>
+      <c r="O13">
+        <v>1000</v>
+      </c>
+      <c r="P13">
+        <v>1000</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
@@ -1657,6 +1801,18 @@
       <c r="J14" t="s">
         <v>28</v>
       </c>
+      <c r="M14">
+        <v>1000</v>
+      </c>
+      <c r="N14">
+        <v>1000</v>
+      </c>
+      <c r="O14">
+        <v>1000</v>
+      </c>
+      <c r="P14">
+        <v>1000</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -1689,6 +1845,18 @@
       <c r="J15" t="s">
         <v>61</v>
       </c>
+      <c r="M15">
+        <v>1000</v>
+      </c>
+      <c r="N15">
+        <v>1000</v>
+      </c>
+      <c r="O15">
+        <v>1000</v>
+      </c>
+      <c r="P15">
+        <v>1000</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
@@ -1724,8 +1892,20 @@
       <c r="L16" t="s">
         <v>63</v>
       </c>
+      <c r="M16">
+        <v>1000</v>
+      </c>
+      <c r="N16">
+        <v>1000</v>
+      </c>
+      <c r="O16">
+        <v>1000</v>
+      </c>
+      <c r="P16">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1756,8 +1936,20 @@
       <c r="J17" t="s">
         <v>46</v>
       </c>
+      <c r="M17">
+        <v>1000</v>
+      </c>
+      <c r="N17">
+        <v>1000</v>
+      </c>
+      <c r="O17">
+        <v>1000</v>
+      </c>
+      <c r="P17">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1787,6 +1979,18 @@
       </c>
       <c r="J18" t="s">
         <v>66</v>
+      </c>
+      <c r="M18">
+        <v>1000</v>
+      </c>
+      <c r="N18">
+        <v>1000</v>
+      </c>
+      <c r="O18">
+        <v>1000</v>
+      </c>
+      <c r="P18">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
     <t>target4</t>
   </si>
   <si>
-    <t>05_16</t>
+    <t>05_16上午</t>
   </si>
   <si>
     <t>doWork1_1</t>
@@ -88,7 +88,7 @@
     <t>cardFirstEnd</t>
   </si>
   <si>
-    <t>05_17</t>
+    <t>05_16下午</t>
   </si>
   <si>
     <t>doWork1_2</t>

--- a/day.xlsx
+++ b/day.xlsx
@@ -1253,16 +1253,16 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="N2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="O2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="P2">
-        <v>1000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1297,16 +1297,16 @@
         <v>21</v>
       </c>
       <c r="M3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="N3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="O3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="P3">
-        <v>1000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1344,16 +1344,16 @@
         <v>25</v>
       </c>
       <c r="M4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="O4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>1000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1391,16 +1391,16 @@
         <v>29</v>
       </c>
       <c r="M5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="O5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="P5">
-        <v>1000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1435,16 +1435,16 @@
         <v>32</v>
       </c>
       <c r="M6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="O6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>1000</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1482,16 +1482,16 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="N7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="O7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="P7">
-        <v>1000</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1529,16 +1529,16 @@
         <v>40</v>
       </c>
       <c r="M8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="N8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="O8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="P8">
-        <v>1000</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1573,16 +1573,16 @@
         <v>43</v>
       </c>
       <c r="M9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="N9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="O9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="P9">
-        <v>1000</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1620,16 +1620,16 @@
         <v>47</v>
       </c>
       <c r="M10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="N10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="O10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="P10">
-        <v>1000</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1664,16 +1664,16 @@
         <v>50</v>
       </c>
       <c r="M11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="N11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="O11">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="P11">
-        <v>1000</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1711,16 +1711,16 @@
         <v>54</v>
       </c>
       <c r="M12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="N12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="O12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="P12">
-        <v>1000</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1758,16 +1758,16 @@
         <v>58</v>
       </c>
       <c r="M13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="N13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="O13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="P13">
-        <v>1000</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1802,16 +1802,16 @@
         <v>28</v>
       </c>
       <c r="M14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="N14">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="O14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="P14">
-        <v>1000</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1846,16 +1846,16 @@
         <v>61</v>
       </c>
       <c r="M15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="N15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="O15">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="P15">
-        <v>1000</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1893,16 +1893,16 @@
         <v>63</v>
       </c>
       <c r="M16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="N16">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="O16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="P16">
-        <v>1000</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1937,16 +1937,16 @@
         <v>46</v>
       </c>
       <c r="M17">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="N17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="O17">
-        <v>1000</v>
+        <v>33</v>
       </c>
       <c r="P17">
-        <v>1000</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1981,16 +1981,16 @@
         <v>66</v>
       </c>
       <c r="M18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="N18">
-        <v>1000</v>
+        <v>33</v>
       </c>
       <c r="O18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="P18">
-        <v>1000</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>day</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>target4</t>
+  </si>
+  <si>
+    <t>targetCharm</t>
   </si>
   <si>
     <t>05_16上午</t>
@@ -1160,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="4" max="5" width="13" customWidth="1"/>
@@ -1171,7 +1174,7 @@
     <col min="12" max="12" width="14.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1220,19 +1223,22 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>0.8</v>
@@ -1250,33 +1256,36 @@
         <v>2</v>
       </c>
       <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2">
+        <v>24</v>
+      </c>
+      <c r="O2">
         <v>18</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-      <c r="N2">
-        <v>11</v>
-      </c>
-      <c r="O2">
-        <v>12</v>
       </c>
       <c r="P2">
         <v>13</v>
       </c>
+      <c r="Q2">
+        <v>135</v>
+      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>0.8</v>
@@ -1294,33 +1303,36 @@
         <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="O3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P3">
         <v>13</v>
       </c>
+      <c r="Q3">
+        <v>135</v>
+      </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>0.8</v>
@@ -1338,36 +1350,39 @@
         <v>2</v>
       </c>
       <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
         <v>24</v>
       </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
-        <v>11</v>
-      </c>
       <c r="O4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P4">
         <v>13</v>
       </c>
+      <c r="Q4">
+        <v>135</v>
+      </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>0.6</v>
@@ -1385,36 +1400,39 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N5">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="O5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P5">
         <v>13</v>
       </c>
+      <c r="Q5">
+        <v>135</v>
+      </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>160</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0.6</v>
@@ -1432,33 +1450,33 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N6">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="P6">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -1476,36 +1494,36 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="N7">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="O7">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="P7">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -1523,36 +1541,36 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
+        <v>80</v>
+      </c>
+      <c r="N8">
+        <v>120</v>
+      </c>
+      <c r="O8">
         <v>40</v>
-      </c>
-      <c r="M8">
-        <v>22</v>
-      </c>
-      <c r="N8">
-        <v>23</v>
-      </c>
-      <c r="O8">
-        <v>24</v>
       </c>
       <c r="P8">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9">
         <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1570,33 +1588,33 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M9">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="N9">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="O9">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="P9">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>300</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10">
         <v>0.4</v>
@@ -1614,36 +1632,36 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M10">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="N10">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="O10">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="P10">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>300</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>0.4</v>
@@ -1661,33 +1679,33 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="N11">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="O11">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="P11">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>300</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>0.4</v>
@@ -1705,36 +1723,36 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M12">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="N12">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="O12">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="P12">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13">
         <v>300</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1752,36 +1770,36 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M13">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="N13">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="O13">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="P13">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14">
         <v>300</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <v>0.4</v>
@@ -1799,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M14">
         <v>28</v>
@@ -1814,18 +1832,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15">
         <v>300</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>0.4</v>
@@ -1843,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M15">
         <v>29</v>
@@ -1858,18 +1876,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16">
         <v>300</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16">
         <v>0.4</v>
@@ -1887,10 +1905,10 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M16">
         <v>30</v>
@@ -1910,13 +1928,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <v>300</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17">
         <v>0.4</v>
@@ -1934,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M17">
         <v>31</v>
@@ -1954,13 +1972,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18">
         <v>0.4</v>
@@ -1978,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M18">
         <v>32</v>

--- a/day.xlsx
+++ b/day.xlsx
@@ -1235,7 +1235,7 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1271,7 +1271,8 @@
         <v>13</v>
       </c>
       <c r="Q2">
-        <v>135</v>
+        <f>M2*15</f>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -1282,7 +1283,7 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1318,7 +1319,8 @@
         <v>13</v>
       </c>
       <c r="Q3">
-        <v>135</v>
+        <f t="shared" ref="Q3:Q13" si="0">M3*15</f>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1329,7 +1331,7 @@
         <v>23</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -1368,7 +1370,8 @@
         <v>13</v>
       </c>
       <c r="Q4">
-        <v>135</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1379,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="C5">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -1418,7 +1421,8 @@
         <v>13</v>
       </c>
       <c r="Q5">
-        <v>135</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -1429,7 +1433,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1463,6 +1467,10 @@
       </c>
       <c r="P6">
         <v>23</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1473,7 +1481,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
@@ -1510,6 +1518,10 @@
       </c>
       <c r="P7">
         <v>24</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1520,7 +1532,7 @@
         <v>38</v>
       </c>
       <c r="C8">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
@@ -1557,6 +1569,10 @@
       </c>
       <c r="P8">
         <v>25</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1567,7 +1583,7 @@
         <v>42</v>
       </c>
       <c r="C9">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
@@ -1601,6 +1617,10 @@
       </c>
       <c r="P9">
         <v>26</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>1800</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1611,7 +1631,7 @@
         <v>45</v>
       </c>
       <c r="C10">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -1648,6 +1668,10 @@
       </c>
       <c r="P10">
         <v>27</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>1800</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1658,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="C11">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -1692,6 +1716,10 @@
       </c>
       <c r="P11">
         <v>28</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>1800</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1702,7 +1730,7 @@
         <v>52</v>
       </c>
       <c r="C12">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -1739,6 +1767,10 @@
       </c>
       <c r="P12">
         <v>29</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>1800</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1749,7 +1781,7 @@
         <v>56</v>
       </c>
       <c r="C13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -1786,6 +1818,10 @@
       </c>
       <c r="P13">
         <v>30</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>1800</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1796,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="C14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
@@ -1830,6 +1866,10 @@
       </c>
       <c r="P14">
         <v>31</v>
+      </c>
+      <c r="Q14">
+        <f>M14*15</f>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1840,7 +1880,7 @@
         <v>61</v>
       </c>
       <c r="C15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
@@ -1874,6 +1914,10 @@
       </c>
       <c r="P15">
         <v>32</v>
+      </c>
+      <c r="Q15">
+        <f>M15*15</f>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1884,7 +1928,7 @@
         <v>63</v>
       </c>
       <c r="C16">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
@@ -1922,8 +1966,12 @@
       <c r="P16">
         <v>33</v>
       </c>
+      <c r="Q16">
+        <f>M16*15</f>
+        <v>450</v>
+      </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1931,7 +1979,7 @@
         <v>65</v>
       </c>
       <c r="C17">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
@@ -1966,8 +2014,12 @@
       <c r="P17">
         <v>34</v>
       </c>
+      <c r="Q17">
+        <f>M17*15</f>
+        <v>465</v>
+      </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1975,7 +2027,7 @@
         <v>66</v>
       </c>
       <c r="C18">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -2009,6 +2061,10 @@
       </c>
       <c r="P18">
         <v>35</v>
+      </c>
+      <c r="Q18">
+        <f>M18*15</f>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11430"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
     <t>targetCharm</t>
   </si>
   <si>
-    <t>05_16上午</t>
+    <t>05_16</t>
   </si>
   <si>
     <t>doWork1_1</t>
@@ -91,7 +91,7 @@
     <t>cardFirstEnd</t>
   </si>
   <si>
-    <t>05_16下午</t>
+    <t>05_17</t>
   </si>
   <si>
     <t>doWork1_2</t>
@@ -1166,6 +1166,7 @@
   <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
+    <col min="3" max="3" width="11.4545454545455" customWidth="1"/>
     <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="16.2727272727273" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -1319,7 +1320,7 @@
         <v>13</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q13" si="0">M3*15</f>
+        <f t="shared" ref="Q3:Q18" si="0">M3*15</f>
         <v>300</v>
       </c>
     </row>
@@ -1868,7 +1869,7 @@
         <v>31</v>
       </c>
       <c r="Q14">
-        <f>M14*15</f>
+        <f t="shared" si="0"/>
         <v>420</v>
       </c>
     </row>
@@ -1916,7 +1917,7 @@
         <v>32</v>
       </c>
       <c r="Q15">
-        <f>M15*15</f>
+        <f t="shared" si="0"/>
         <v>435</v>
       </c>
     </row>
@@ -1967,7 +1968,7 @@
         <v>33</v>
       </c>
       <c r="Q16">
-        <f>M16*15</f>
+        <f t="shared" si="0"/>
         <v>450</v>
       </c>
     </row>
@@ -2015,7 +2016,7 @@
         <v>34</v>
       </c>
       <c r="Q17">
-        <f>M17*15</f>
+        <f t="shared" si="0"/>
         <v>465</v>
       </c>
     </row>
@@ -2063,7 +2064,7 @@
         <v>35</v>
       </c>
       <c r="Q18">
-        <f>M18*15</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
     </row>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
   <si>
     <t>day</t>
   </si>
@@ -82,157 +82,160 @@
     <t>targetCharm</t>
   </si>
   <si>
+    <t>05_15</t>
+  </si>
+  <si>
+    <t>doWork1_1</t>
+  </si>
+  <si>
+    <t>cardFirstEnd</t>
+  </si>
+  <si>
     <t>05_16</t>
   </si>
   <si>
-    <t>doWork1_1</t>
-  </si>
-  <si>
-    <t>cardFirstEnd</t>
+    <t>doWork1_2</t>
+  </si>
+  <si>
+    <t>normalEnd1_2</t>
   </si>
   <si>
     <t>05_17</t>
   </si>
   <si>
-    <t>doWork1_2</t>
-  </si>
-  <si>
-    <t>normalEnd1_2</t>
+    <t>doWork1_3</t>
+  </si>
+  <si>
+    <t>simpleEnd1_1</t>
+  </si>
+  <si>
+    <t>special1_1</t>
   </si>
   <si>
     <t>05_18</t>
   </si>
   <si>
-    <t>doWork1_3</t>
-  </si>
-  <si>
-    <t>simpleEnd1_1</t>
-  </si>
-  <si>
-    <t>special1_1</t>
+    <t>doWork1_4</t>
+  </si>
+  <si>
+    <t>simpleEnd1_2</t>
+  </si>
+  <si>
+    <t>failed1_1</t>
   </si>
   <si>
     <t>05_19</t>
   </si>
   <si>
-    <t>doWork1_4</t>
-  </si>
-  <si>
-    <t>simpleEnd1_2</t>
-  </si>
-  <si>
-    <t>failed1_1</t>
+    <t>doWork2_1</t>
+  </si>
+  <si>
+    <t>normalEnd1_3</t>
   </si>
   <si>
     <t>05_20</t>
   </si>
   <si>
-    <t>doWork2_1</t>
-  </si>
-  <si>
-    <t>normalEnd1_3</t>
+    <t>doWork2_2</t>
+  </si>
+  <si>
+    <t>simpleEnd1_4</t>
+  </si>
+  <si>
+    <t>special1_2</t>
   </si>
   <si>
     <t>05_21</t>
   </si>
   <si>
-    <t>doWork2_2</t>
-  </si>
-  <si>
-    <t>simpleEnd1_4</t>
-  </si>
-  <si>
-    <t>special1_2</t>
+    <t>doWork2_3</t>
+  </si>
+  <si>
+    <t>normalEnd1_4</t>
+  </si>
+  <si>
+    <t>failed1_2</t>
   </si>
   <si>
     <t>05_22</t>
   </si>
   <si>
-    <t>doWork2_3</t>
-  </si>
-  <si>
-    <t>normalEnd1_4</t>
-  </si>
-  <si>
-    <t>failed1_2</t>
+    <t>doWork2_4</t>
+  </si>
+  <si>
+    <t>normalEnd1_5</t>
   </si>
   <si>
     <t>05_23</t>
   </si>
   <si>
-    <t>doWork2_4</t>
-  </si>
-  <si>
-    <t>normalEnd1_5</t>
+    <t>doWork3_1</t>
+  </si>
+  <si>
+    <t>simpleEnd1_5</t>
+  </si>
+  <si>
+    <t>special1_3</t>
   </si>
   <si>
     <t>05_24</t>
   </si>
   <si>
-    <t>doWork3_1</t>
-  </si>
-  <si>
-    <t>simpleEnd1_5</t>
-  </si>
-  <si>
-    <t>special1_3</t>
+    <t>doWork3_2</t>
+  </si>
+  <si>
+    <t>normalEnd1_6</t>
   </si>
   <si>
     <t>05_25</t>
   </si>
   <si>
-    <t>doWork3_2</t>
-  </si>
-  <si>
-    <t>normalEnd1_6</t>
+    <t>doWork3_3</t>
+  </si>
+  <si>
+    <t>normalEnd1_7</t>
+  </si>
+  <si>
+    <t>failed1_3</t>
   </si>
   <si>
     <t>05_26</t>
   </si>
   <si>
-    <t>doWork3_3</t>
-  </si>
-  <si>
-    <t>normalEnd1_7</t>
-  </si>
-  <si>
-    <t>failed1_3</t>
+    <t>doWork3_4</t>
+  </si>
+  <si>
+    <t>simpleEnd1_8</t>
+  </si>
+  <si>
+    <t>special1_4</t>
   </si>
   <si>
     <t>05_27</t>
   </si>
   <si>
-    <t>doWork3_4</t>
-  </si>
-  <si>
-    <t>simpleEnd1_8</t>
-  </si>
-  <si>
-    <t>special1_4</t>
-  </si>
-  <si>
     <t>05_28</t>
   </si>
   <si>
+    <t>simpleEnd1_3</t>
+  </si>
+  <si>
     <t>05_29</t>
   </si>
   <si>
-    <t>simpleEnd1_3</t>
+    <t>failed1_4</t>
   </si>
   <si>
     <t>05_30</t>
   </si>
   <si>
-    <t>failed1_4</t>
-  </si>
-  <si>
     <t>05_31</t>
   </si>
   <si>
+    <t>simpleEnd1_6</t>
+  </si>
+  <si>
     <t>06_01</t>
-  </si>
-  <si>
-    <t>simpleEnd1_6</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="11.4545454545455" customWidth="1"/>
@@ -2066,6 +2069,11 @@
       <c r="Q18">
         <f t="shared" si="0"/>
         <v>480</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="B19" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
     <t>day</t>
   </si>
@@ -82,157 +82,160 @@
     <t>targetCharm</t>
   </si>
   <si>
+    <t>05_14</t>
+  </si>
+  <si>
+    <t>doWork1_1</t>
+  </si>
+  <si>
+    <t>cardFirstEnd</t>
+  </si>
+  <si>
     <t>05_15</t>
   </si>
   <si>
-    <t>doWork1_1</t>
-  </si>
-  <si>
-    <t>cardFirstEnd</t>
+    <t>doWork1_2</t>
+  </si>
+  <si>
+    <t>normalEnd1_2</t>
   </si>
   <si>
     <t>05_16</t>
   </si>
   <si>
-    <t>doWork1_2</t>
-  </si>
-  <si>
-    <t>normalEnd1_2</t>
+    <t>doWork1_3</t>
+  </si>
+  <si>
+    <t>simpleEnd1_1</t>
+  </si>
+  <si>
+    <t>special1_1</t>
   </si>
   <si>
     <t>05_17</t>
   </si>
   <si>
-    <t>doWork1_3</t>
-  </si>
-  <si>
-    <t>simpleEnd1_1</t>
-  </si>
-  <si>
-    <t>special1_1</t>
+    <t>doWork1_4</t>
+  </si>
+  <si>
+    <t>simpleEnd1_2</t>
+  </si>
+  <si>
+    <t>failed1_1</t>
   </si>
   <si>
     <t>05_18</t>
   </si>
   <si>
-    <t>doWork1_4</t>
-  </si>
-  <si>
-    <t>simpleEnd1_2</t>
-  </si>
-  <si>
-    <t>failed1_1</t>
+    <t>doWork2_1</t>
+  </si>
+  <si>
+    <t>normalEnd1_3</t>
   </si>
   <si>
     <t>05_19</t>
   </si>
   <si>
-    <t>doWork2_1</t>
-  </si>
-  <si>
-    <t>normalEnd1_3</t>
+    <t>doWork2_2</t>
+  </si>
+  <si>
+    <t>simpleEnd1_4</t>
+  </si>
+  <si>
+    <t>special1_2</t>
   </si>
   <si>
     <t>05_20</t>
   </si>
   <si>
-    <t>doWork2_2</t>
-  </si>
-  <si>
-    <t>simpleEnd1_4</t>
-  </si>
-  <si>
-    <t>special1_2</t>
+    <t>doWork2_3</t>
+  </si>
+  <si>
+    <t>normalEnd1_4</t>
+  </si>
+  <si>
+    <t>failed1_2</t>
   </si>
   <si>
     <t>05_21</t>
   </si>
   <si>
-    <t>doWork2_3</t>
-  </si>
-  <si>
-    <t>normalEnd1_4</t>
-  </si>
-  <si>
-    <t>failed1_2</t>
+    <t>doWork2_4</t>
+  </si>
+  <si>
+    <t>normalEnd1_5</t>
   </si>
   <si>
     <t>05_22</t>
   </si>
   <si>
-    <t>doWork2_4</t>
-  </si>
-  <si>
-    <t>normalEnd1_5</t>
+    <t>doWork3_1</t>
+  </si>
+  <si>
+    <t>simpleEnd1_5</t>
+  </si>
+  <si>
+    <t>special1_3</t>
   </si>
   <si>
     <t>05_23</t>
   </si>
   <si>
-    <t>doWork3_1</t>
-  </si>
-  <si>
-    <t>simpleEnd1_5</t>
-  </si>
-  <si>
-    <t>special1_3</t>
+    <t>doWork3_2</t>
+  </si>
+  <si>
+    <t>normalEnd1_6</t>
   </si>
   <si>
     <t>05_24</t>
   </si>
   <si>
-    <t>doWork3_2</t>
-  </si>
-  <si>
-    <t>normalEnd1_6</t>
+    <t>doWork3_3</t>
+  </si>
+  <si>
+    <t>normalEnd1_7</t>
+  </si>
+  <si>
+    <t>failed1_3</t>
   </si>
   <si>
     <t>05_25</t>
   </si>
   <si>
-    <t>doWork3_3</t>
-  </si>
-  <si>
-    <t>normalEnd1_7</t>
-  </si>
-  <si>
-    <t>failed1_3</t>
+    <t>doWork3_4</t>
+  </si>
+  <si>
+    <t>simpleEnd1_8</t>
+  </si>
+  <si>
+    <t>special1_4</t>
   </si>
   <si>
     <t>05_26</t>
   </si>
   <si>
-    <t>doWork3_4</t>
-  </si>
-  <si>
-    <t>simpleEnd1_8</t>
-  </si>
-  <si>
-    <t>special1_4</t>
-  </si>
-  <si>
     <t>05_27</t>
   </si>
   <si>
+    <t>simpleEnd1_3</t>
+  </si>
+  <si>
     <t>05_28</t>
   </si>
   <si>
-    <t>simpleEnd1_3</t>
+    <t>failed1_4</t>
   </si>
   <si>
     <t>05_29</t>
   </si>
   <si>
-    <t>failed1_4</t>
-  </si>
-  <si>
     <t>05_30</t>
   </si>
   <si>
+    <t>simpleEnd1_6</t>
+  </si>
+  <si>
     <t>05_31</t>
-  </si>
-  <si>
-    <t>simpleEnd1_6</t>
   </si>
   <si>
     <t>06_01</t>
@@ -1166,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="11.4545454545455" customWidth="1"/>
@@ -2074,6 +2077,11 @@
     <row r="19" spans="1:17">
       <c r="B19" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="B20" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <t>05_14</t>
   </si>
   <si>
-    <t>doWork1_1</t>
+    <t>start0_1</t>
   </si>
   <si>
     <t>cardFirstEnd</t>
@@ -1275,7 +1275,8 @@
         <v>18</v>
       </c>
       <c r="P2">
-        <v>13</v>
+        <f>M2*2.5</f>
+        <v>50</v>
       </c>
       <c r="Q2">
         <f>M2*15</f>
@@ -1323,10 +1324,11 @@
         <v>18</v>
       </c>
       <c r="P3">
-        <v>13</v>
+        <f t="shared" ref="P3:P13" si="0">M3*2.5</f>
+        <v>50</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q18" si="0">M3*15</f>
+        <f t="shared" ref="Q3:Q18" si="1">M3*15</f>
         <v>300</v>
       </c>
     </row>
@@ -1374,10 +1376,11 @@
         <v>18</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
@@ -1425,10 +1428,11 @@
         <v>18</v>
       </c>
       <c r="P5">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
@@ -1473,10 +1477,11 @@
         <v>40</v>
       </c>
       <c r="P6">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
@@ -1524,10 +1529,11 @@
         <v>40</v>
       </c>
       <c r="P7">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
@@ -1575,10 +1581,11 @@
         <v>40</v>
       </c>
       <c r="P8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
@@ -1623,10 +1630,11 @@
         <v>120</v>
       </c>
       <c r="P9">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
@@ -1674,10 +1682,11 @@
         <v>120</v>
       </c>
       <c r="P10">
-        <v>27</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
@@ -1722,10 +1731,11 @@
         <v>120</v>
       </c>
       <c r="P11">
-        <v>28</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
@@ -1773,10 +1783,11 @@
         <v>120</v>
       </c>
       <c r="P12">
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
@@ -1824,10 +1835,11 @@
         <v>120</v>
       </c>
       <c r="P13">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
@@ -1875,7 +1887,7 @@
         <v>31</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>420</v>
       </c>
     </row>
@@ -1923,7 +1935,7 @@
         <v>32</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>435</v>
       </c>
     </row>
@@ -1974,7 +1986,7 @@
         <v>33</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
     </row>
@@ -2022,7 +2034,7 @@
         <v>34</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>465</v>
       </c>
     </row>
@@ -2070,7 +2082,7 @@
         <v>35</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>480</v>
       </c>
     </row>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
   <si>
     <t>day</t>
   </si>
@@ -100,7 +100,7 @@
     <t>normalEnd1_2</t>
   </si>
   <si>
-    <t>05_16</t>
+    <t>05_17</t>
   </si>
   <si>
     <t>doWork1_3</t>
@@ -112,7 +112,7 @@
     <t>special1_1</t>
   </si>
   <si>
-    <t>05_17</t>
+    <t>05_18</t>
   </si>
   <si>
     <t>doWork1_4</t>
@@ -124,7 +124,7 @@
     <t>failed1_1</t>
   </si>
   <si>
-    <t>05_18</t>
+    <t>05_19</t>
   </si>
   <si>
     <t>doWork2_1</t>
@@ -133,7 +133,7 @@
     <t>normalEnd1_3</t>
   </si>
   <si>
-    <t>05_19</t>
+    <t>05_20</t>
   </si>
   <si>
     <t>doWork2_2</t>
@@ -145,7 +145,7 @@
     <t>special1_2</t>
   </si>
   <si>
-    <t>05_20</t>
+    <t>05_21</t>
   </si>
   <si>
     <t>doWork2_3</t>
@@ -157,7 +157,7 @@
     <t>failed1_2</t>
   </si>
   <si>
-    <t>05_21</t>
+    <t>05_22</t>
   </si>
   <si>
     <t>doWork2_4</t>
@@ -166,7 +166,7 @@
     <t>normalEnd1_5</t>
   </si>
   <si>
-    <t>05_22</t>
+    <t>05_23</t>
   </si>
   <si>
     <t>doWork3_1</t>
@@ -178,16 +178,13 @@
     <t>special1_3</t>
   </si>
   <si>
-    <t>05_23</t>
+    <t>05_24</t>
   </si>
   <si>
     <t>doWork3_2</t>
   </si>
   <si>
     <t>normalEnd1_6</t>
-  </si>
-  <si>
-    <t>05_24</t>
   </si>
   <si>
     <t>doWork3_3</t>
@@ -1744,13 +1741,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>0.4</v>
@@ -1768,10 +1765,10 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" t="s">
         <v>54</v>
-      </c>
-      <c r="L12" t="s">
-        <v>55</v>
       </c>
       <c r="M12">
         <v>120</v>
@@ -1796,13 +1793,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1820,10 +1817,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
         <v>58</v>
-      </c>
-      <c r="K13" t="s">
-        <v>59</v>
       </c>
       <c r="M13">
         <v>120</v>
@@ -1848,7 +1845,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -1896,7 +1893,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -1920,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M15">
         <v>29</v>
@@ -1944,7 +1941,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -1971,7 +1968,7 @@
         <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M16">
         <v>30</v>
@@ -1995,7 +1992,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -2043,7 +2040,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -2067,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M18">
         <v>32</v>
@@ -2088,12 +2085,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -82,16 +82,16 @@
     <t>targetCharm</t>
   </si>
   <si>
-    <t>05_14</t>
+    <t>09_01</t>
   </si>
   <si>
     <t>start0_1</t>
   </si>
   <si>
-    <t>cardFirstEnd</t>
-  </si>
-  <si>
-    <t>05_15</t>
+    <t>day9_2</t>
+  </si>
+  <si>
+    <t>09_02</t>
   </si>
   <si>
     <t>doWork1_2</t>
@@ -100,7 +100,7 @@
     <t>normalEnd1_2</t>
   </si>
   <si>
-    <t>05_17</t>
+    <t>09_03</t>
   </si>
   <si>
     <t>doWork1_3</t>
@@ -112,7 +112,7 @@
     <t>special1_1</t>
   </si>
   <si>
-    <t>05_18</t>
+    <t>09_04</t>
   </si>
   <si>
     <t>doWork1_4</t>
@@ -121,10 +121,13 @@
     <t>simpleEnd1_2</t>
   </si>
   <si>
+    <t>第一次周末，接入start1_2</t>
+  </si>
+  <si>
     <t>failed1_1</t>
   </si>
   <si>
-    <t>05_19</t>
+    <t>09_07</t>
   </si>
   <si>
     <t>doWork2_1</t>
@@ -133,7 +136,7 @@
     <t>normalEnd1_3</t>
   </si>
   <si>
-    <t>05_20</t>
+    <t>09_06</t>
   </si>
   <si>
     <t>doWork2_2</t>
@@ -145,9 +148,6 @@
     <t>special1_2</t>
   </si>
   <si>
-    <t>05_21</t>
-  </si>
-  <si>
     <t>doWork2_3</t>
   </si>
   <si>
@@ -157,7 +157,7 @@
     <t>failed1_2</t>
   </si>
   <si>
-    <t>05_22</t>
+    <t>09_08</t>
   </si>
   <si>
     <t>doWork2_4</t>
@@ -166,7 +166,7 @@
     <t>normalEnd1_5</t>
   </si>
   <si>
-    <t>05_23</t>
+    <t>09_09</t>
   </si>
   <si>
     <t>doWork3_1</t>
@@ -178,7 +178,7 @@
     <t>special1_3</t>
   </si>
   <si>
-    <t>05_24</t>
+    <t>09_10</t>
   </si>
   <si>
     <t>doWork3_2</t>
@@ -187,16 +187,22 @@
     <t>normalEnd1_6</t>
   </si>
   <si>
+    <t>09_11</t>
+  </si>
+  <si>
     <t>doWork3_3</t>
   </si>
   <si>
     <t>normalEnd1_7</t>
   </si>
   <si>
+    <t>第二次周末，接入剧情2</t>
+  </si>
+  <si>
     <t>failed1_3</t>
   </si>
   <si>
-    <t>05_25</t>
+    <t>09_14</t>
   </si>
   <si>
     <t>doWork3_4</t>
@@ -208,34 +214,28 @@
     <t>special1_4</t>
   </si>
   <si>
-    <t>05_26</t>
-  </si>
-  <si>
-    <t>05_27</t>
+    <t>09_15</t>
+  </si>
+  <si>
+    <t>09_16</t>
   </si>
   <si>
     <t>simpleEnd1_3</t>
   </si>
   <si>
-    <t>05_28</t>
+    <t>09_17</t>
   </si>
   <si>
     <t>failed1_4</t>
   </si>
   <si>
-    <t>05_29</t>
-  </si>
-  <si>
-    <t>05_30</t>
+    <t>09_18</t>
+  </si>
+  <si>
+    <t>09_19</t>
   </si>
   <si>
     <t>simpleEnd1_6</t>
-  </si>
-  <si>
-    <t>05_31</t>
-  </si>
-  <si>
-    <t>06_01</t>
   </si>
 </sst>
 </file>
@@ -401,12 +401,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -727,7 +733,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -751,16 +757,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -769,90 +775,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1166,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="11.4545454545455" customWidth="1"/>
@@ -1174,11 +1183,11 @@
     <col min="6" max="6" width="16.2727272727273" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="10" max="10" width="14.8181818181818" customWidth="1"/>
-    <col min="11" max="11" width="14.4545454545455" customWidth="1"/>
-    <col min="12" max="12" width="14.7272727272727" customWidth="1"/>
+    <col min="11" max="12" width="14.4545454545455" customWidth="1"/>
+    <col min="13" max="13" width="14.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1209,29 +1218,29 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1262,25 +1271,25 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>20</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>24</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>18</v>
       </c>
-      <c r="P2">
-        <f>M2*2.5</f>
+      <c r="Q2">
+        <f>N2*2.5</f>
         <v>50</v>
       </c>
-      <c r="Q2">
-        <f>M2*15</f>
+      <c r="R2">
+        <f>N2*15</f>
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1311,25 +1320,25 @@
       <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>20</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>24</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>18</v>
       </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P13" si="0">M3*2.5</f>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q13" si="0">N3*2.5</f>
         <v>50</v>
       </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q18" si="1">M3*15</f>
+      <c r="R3">
+        <f t="shared" ref="R3:R18" si="1">N3*15</f>
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1360,91 +1369,94 @@
       <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>26</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>20</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>24</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>18</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5">
+    <row r="5" s="1" customFormat="1" spans="1:18">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>60</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.4</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L5" t="s">
+      <c r="K5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="1">
         <v>20</v>
       </c>
-      <c r="N5">
+      <c r="O5" s="1">
         <v>24</v>
       </c>
-      <c r="O5">
+      <c r="P5" s="1">
         <v>18</v>
       </c>
-      <c r="P5">
+      <c r="Q5" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="Q5">
+      <c r="R5" s="1">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0.6</v>
@@ -1462,38 +1474,38 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6">
+        <v>34</v>
+      </c>
+      <c r="N6">
         <v>80</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>120</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>40</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -1511,35 +1523,35 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" t="s">
         <v>37</v>
       </c>
-      <c r="M7">
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7">
         <v>80</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>120</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>40</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1565,28 +1577,28 @@
       <c r="J8" t="s">
         <v>40</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>41</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>80</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>120</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>40</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1617,25 +1629,25 @@
       <c r="J9" t="s">
         <v>44</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>120</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>160</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>120</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1666,28 +1678,28 @@
       <c r="J10" t="s">
         <v>47</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>48</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>120</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>160</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>120</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1718,88 +1730,91 @@
       <c r="J11" t="s">
         <v>51</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>120</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>160</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>120</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
-      <c r="A12">
+    <row r="12" s="1" customFormat="1" spans="1:18">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="1">
         <v>200</v>
       </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1">
         <v>0.4</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>0.4</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>0.2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>4</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1</v>
       </c>
-      <c r="J12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="J12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M12">
+      <c r="K12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="1">
         <v>120</v>
       </c>
-      <c r="N12">
+      <c r="O12" s="1">
         <v>160</v>
       </c>
-      <c r="O12">
+      <c r="P12" s="1">
         <v>120</v>
       </c>
-      <c r="P12">
+      <c r="Q12" s="1">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q12">
+      <c r="R12" s="1">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1817,35 +1832,35 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13">
+        <v>59</v>
+      </c>
+      <c r="L13" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13">
         <v>120</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>160</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>120</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -1871,29 +1886,29 @@
       <c r="J14" t="s">
         <v>29</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>28</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>29</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>30</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>31</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -1917,31 +1932,31 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15">
+        <v>63</v>
+      </c>
+      <c r="N15">
         <v>29</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>30</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>31</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>32</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <f t="shared" si="1"/>
         <v>435</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -1965,34 +1980,34 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M16">
+        <v>37</v>
+      </c>
+      <c r="M16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16">
         <v>30</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>31</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>32</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>33</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -2018,29 +2033,29 @@
       <c r="J17" t="s">
         <v>47</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>31</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>32</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>33</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>34</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -2064,33 +2079,23 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
-      </c>
-      <c r="M18">
+        <v>68</v>
+      </c>
+      <c r="N18">
         <v>32</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>33</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>34</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>35</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <f t="shared" si="1"/>
         <v>480</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="B19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="B20" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>day</t>
   </si>
@@ -97,7 +97,7 @@
     <t>doWork1_2</t>
   </si>
   <si>
-    <t>normalEnd1_2</t>
+    <t>day9_3</t>
   </si>
   <si>
     <t>09_03</t>
@@ -106,7 +106,7 @@
     <t>doWork1_3</t>
   </si>
   <si>
-    <t>simpleEnd1_1</t>
+    <t>day9_4</t>
   </si>
   <si>
     <t>special1_1</t>
@@ -118,121 +118,133 @@
     <t>doWork1_4</t>
   </si>
   <si>
+    <t>day9_7</t>
+  </si>
+  <si>
+    <t>第一次周末，接入start1_2</t>
+  </si>
+  <si>
+    <t>failed1_1</t>
+  </si>
+  <si>
+    <t>09_07</t>
+  </si>
+  <si>
+    <t>doWork2_1</t>
+  </si>
+  <si>
+    <t>day9_8</t>
+  </si>
+  <si>
+    <t>09_08</t>
+  </si>
+  <si>
+    <t>doWork2_2</t>
+  </si>
+  <si>
+    <t>day9_9</t>
+  </si>
+  <si>
+    <t>special1_2</t>
+  </si>
+  <si>
+    <t>09_09</t>
+  </si>
+  <si>
+    <t>doWork2_3</t>
+  </si>
+  <si>
+    <t>day9_10</t>
+  </si>
+  <si>
+    <t>failed1_2</t>
+  </si>
+  <si>
+    <t>09_10</t>
+  </si>
+  <si>
+    <t>doWork2_4</t>
+  </si>
+  <si>
+    <t>day9_11</t>
+  </si>
+  <si>
+    <t>09_11</t>
+  </si>
+  <si>
+    <t>doWork3_1</t>
+  </si>
+  <si>
+    <t>day9_12</t>
+  </si>
+  <si>
+    <t>special1_3</t>
+  </si>
+  <si>
+    <t>09_12</t>
+  </si>
+  <si>
+    <t>doWork3_2</t>
+  </si>
+  <si>
+    <t>day9_13</t>
+  </si>
+  <si>
+    <t>09_13</t>
+  </si>
+  <si>
+    <t>doWork3_3</t>
+  </si>
+  <si>
+    <t>day9_16</t>
+  </si>
+  <si>
+    <t>第二次周末，接入剧情2</t>
+  </si>
+  <si>
+    <t>failed1_3</t>
+  </si>
+  <si>
+    <t>09_16</t>
+  </si>
+  <si>
+    <t>doWork3_4</t>
+  </si>
+  <si>
+    <t>simpleEnd1_8</t>
+  </si>
+  <si>
+    <t>special1_4</t>
+  </si>
+  <si>
+    <t>09_17</t>
+  </si>
+  <si>
     <t>simpleEnd1_2</t>
   </si>
   <si>
-    <t>第一次周末，接入start1_2</t>
-  </si>
-  <si>
-    <t>failed1_1</t>
-  </si>
-  <si>
-    <t>09_07</t>
-  </si>
-  <si>
-    <t>doWork2_1</t>
-  </si>
-  <si>
-    <t>normalEnd1_3</t>
-  </si>
-  <si>
-    <t>09_06</t>
-  </si>
-  <si>
-    <t>doWork2_2</t>
+    <t>09_18</t>
+  </si>
+  <si>
+    <t>simpleEnd1_3</t>
+  </si>
+  <si>
+    <t>09_19</t>
   </si>
   <si>
     <t>simpleEnd1_4</t>
   </si>
   <si>
-    <t>special1_2</t>
-  </si>
-  <si>
-    <t>doWork2_3</t>
-  </si>
-  <si>
-    <t>normalEnd1_4</t>
-  </si>
-  <si>
-    <t>failed1_2</t>
-  </si>
-  <si>
-    <t>09_08</t>
-  </si>
-  <si>
-    <t>doWork2_4</t>
-  </si>
-  <si>
-    <t>normalEnd1_5</t>
-  </si>
-  <si>
-    <t>09_09</t>
-  </si>
-  <si>
-    <t>doWork3_1</t>
+    <t>failed1_4</t>
+  </si>
+  <si>
+    <t>09_20</t>
   </si>
   <si>
     <t>simpleEnd1_5</t>
   </si>
   <si>
-    <t>special1_3</t>
-  </si>
-  <si>
-    <t>09_10</t>
-  </si>
-  <si>
-    <t>doWork3_2</t>
-  </si>
-  <si>
-    <t>normalEnd1_6</t>
-  </si>
-  <si>
-    <t>09_11</t>
-  </si>
-  <si>
-    <t>doWork3_3</t>
-  </si>
-  <si>
-    <t>normalEnd1_7</t>
-  </si>
-  <si>
-    <t>第二次周末，接入剧情2</t>
-  </si>
-  <si>
-    <t>failed1_3</t>
-  </si>
-  <si>
-    <t>09_14</t>
-  </si>
-  <si>
-    <t>doWork3_4</t>
-  </si>
-  <si>
-    <t>simpleEnd1_8</t>
-  </si>
-  <si>
-    <t>special1_4</t>
-  </si>
-  <si>
-    <t>09_15</t>
-  </si>
-  <si>
-    <t>09_16</t>
-  </si>
-  <si>
-    <t>simpleEnd1_3</t>
-  </si>
-  <si>
-    <t>09_17</t>
-  </si>
-  <si>
-    <t>failed1_4</t>
-  </si>
-  <si>
-    <t>09_18</t>
-  </si>
-  <si>
-    <t>09_19</t>
+    <t>09_21</t>
   </si>
   <si>
     <t>simpleEnd1_6</t>
@@ -1418,7 +1430,7 @@
       <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -1551,13 +1563,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -1575,10 +1587,10 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N8">
         <v>80</v>
@@ -1603,13 +1615,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1627,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N9">
         <v>120</v>
@@ -1652,13 +1664,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10">
         <v>0.4</v>
@@ -1676,10 +1688,10 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10">
         <v>120</v>
@@ -1704,13 +1716,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>0.4</v>
@@ -1728,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N11">
         <v>120</v>
@@ -1753,13 +1765,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1">
         <v>200</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1">
         <v>0.4</v>
@@ -1777,13 +1789,13 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N12" s="1">
         <v>120</v>
@@ -1808,13 +1820,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1832,10 +1844,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N13">
         <v>120</v>
@@ -1860,7 +1872,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -1884,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="N14">
         <v>28</v>
@@ -1908,7 +1920,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -1932,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N15">
         <v>29</v>
@@ -1956,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -1980,10 +1992,10 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="M16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N16">
         <v>30</v>
@@ -2007,7 +2019,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -2031,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="N17">
         <v>31</v>
@@ -2055,7 +2067,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -2079,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N18">
         <v>32</v>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>day</t>
   </si>
@@ -109,9 +109,6 @@
     <t>day9_4</t>
   </si>
   <si>
-    <t>special1_1</t>
-  </si>
-  <si>
     <t>09_04</t>
   </si>
   <si>
@@ -121,9 +118,6 @@
     <t>day9_7</t>
   </si>
   <si>
-    <t>第一次周末，接入start1_2</t>
-  </si>
-  <si>
     <t>failed1_1</t>
   </si>
   <si>
@@ -197,9 +191,6 @@
   </si>
   <si>
     <t>day9_16</t>
-  </si>
-  <si>
-    <t>第二次周末，接入剧情2</t>
   </si>
   <si>
     <t>failed1_3</t>
@@ -1187,7 +1178,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="11.4545454545455" customWidth="1"/>
@@ -1195,11 +1186,11 @@
     <col min="6" max="6" width="16.2727272727273" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="10" max="10" width="14.8181818181818" customWidth="1"/>
-    <col min="11" max="12" width="14.4545454545455" customWidth="1"/>
-    <col min="13" max="13" width="14.7272727272727" customWidth="1"/>
+    <col min="11" max="11" width="14.4545454545455" customWidth="1"/>
+    <col min="12" max="12" width="14.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1230,29 +1221,29 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1283,25 +1274,25 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
       <c r="N2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P2">
-        <v>18</v>
+        <f>M2*2.5</f>
+        <v>50</v>
       </c>
       <c r="Q2">
-        <f>N2*2.5</f>
-        <v>50</v>
-      </c>
-      <c r="R2">
-        <f>N2*15</f>
+        <f>M2*15</f>
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1332,25 +1323,25 @@
       <c r="J3" t="s">
         <v>22</v>
       </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
       <c r="N3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>18</v>
+        <f t="shared" ref="P3:P13" si="0">M3*2.5</f>
+        <v>50</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q13" si="0">N3*2.5</f>
-        <v>50</v>
-      </c>
-      <c r="R3">
-        <f t="shared" ref="R3:R18" si="1">N3*15</f>
+        <f t="shared" ref="Q3:Q18" si="1">M3*15</f>
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1381,39 +1372,37 @@
       <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="L4" t="s">
-        <v>26</v>
+      <c r="K4"/>
+      <c r="M4">
+        <v>20</v>
       </c>
       <c r="N4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>18</v>
-      </c>
-      <c r="Q4">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="R4">
+      <c r="Q4">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:18">
+    <row r="5" s="1" customFormat="1" spans="1:17">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>60</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
         <v>0.6</v>
@@ -1430,45 +1419,42 @@
       <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>31</v>
+      <c r="M5" s="1">
+        <v>20</v>
       </c>
       <c r="N5" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O5" s="1">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P5" s="1">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="R5" s="1">
+      <c r="Q5" s="1">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0.6</v>
@@ -1486,38 +1472,38 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="M6">
+        <v>80</v>
       </c>
       <c r="N6">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="O6">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="P6">
-        <v>40</v>
-      </c>
-      <c r="Q6">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="R6">
+      <c r="Q6">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -1535,41 +1521,41 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
+        <v>80</v>
       </c>
       <c r="N7">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="O7">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="P7">
-        <v>40</v>
-      </c>
-      <c r="Q7">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="R7">
+      <c r="Q7">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -1587,41 +1573,41 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8">
+        <v>80</v>
       </c>
       <c r="N8">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="O8">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="P8">
-        <v>40</v>
-      </c>
-      <c r="Q8">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="R8">
+      <c r="Q8">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1639,38 +1625,38 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="M9">
+        <v>120</v>
       </c>
       <c r="N9">
+        <v>160</v>
+      </c>
+      <c r="O9">
         <v>120</v>
       </c>
-      <c r="O9">
-        <v>160</v>
-      </c>
       <c r="P9">
-        <v>120</v>
-      </c>
-      <c r="Q9">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="R9">
+      <c r="Q9">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10">
         <v>0.4</v>
@@ -1688,41 +1674,41 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="K10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
+        <v>120</v>
       </c>
       <c r="N10">
+        <v>160</v>
+      </c>
+      <c r="O10">
         <v>120</v>
       </c>
-      <c r="O10">
-        <v>160</v>
-      </c>
       <c r="P10">
-        <v>120</v>
-      </c>
-      <c r="Q10">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="R10">
+      <c r="Q10">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>0.4</v>
@@ -1740,38 +1726,38 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>120</v>
       </c>
       <c r="N11">
+        <v>160</v>
+      </c>
+      <c r="O11">
         <v>120</v>
       </c>
-      <c r="O11">
-        <v>160</v>
-      </c>
       <c r="P11">
-        <v>120</v>
-      </c>
-      <c r="Q11">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="R11">
+      <c r="Q11">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:18">
+    <row r="12" s="1" customFormat="1" spans="1:17">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1">
         <v>200</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E12" s="1">
         <v>0.4</v>
@@ -1789,44 +1775,41 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="1">
+        <v>120</v>
       </c>
       <c r="N12" s="1">
+        <v>160</v>
+      </c>
+      <c r="O12" s="1">
         <v>120</v>
       </c>
-      <c r="O12" s="1">
-        <v>160</v>
-      </c>
       <c r="P12" s="1">
-        <v>120</v>
-      </c>
-      <c r="Q12" s="1">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="R12" s="1">
+      <c r="Q12" s="1">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1844,35 +1827,35 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" t="s">
-        <v>61</v>
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13">
+        <v>120</v>
       </c>
       <c r="N13">
+        <v>160</v>
+      </c>
+      <c r="O13">
         <v>120</v>
       </c>
-      <c r="O13">
-        <v>160</v>
-      </c>
       <c r="P13">
-        <v>120</v>
-      </c>
-      <c r="Q13">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="R13">
+      <c r="Q13">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -1896,31 +1879,31 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="M14">
+        <v>28</v>
       </c>
       <c r="N14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q14">
-        <v>31</v>
-      </c>
-      <c r="R14">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -1944,31 +1927,31 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="M15">
+        <v>29</v>
       </c>
       <c r="N15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q15">
-        <v>32</v>
-      </c>
-      <c r="R15">
         <f t="shared" si="1"/>
         <v>435</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -1992,34 +1975,34 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M16" t="s">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="L16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16">
+        <v>30</v>
       </c>
       <c r="N16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q16">
-        <v>33</v>
-      </c>
-      <c r="R16">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -2043,31 +2026,31 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="M17">
+        <v>31</v>
       </c>
       <c r="N17">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P17">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q17">
-        <v>34</v>
-      </c>
-      <c r="R17">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -2091,21 +2074,21 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="M18">
+        <v>32</v>
       </c>
       <c r="N18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P18">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q18">
-        <v>35</v>
-      </c>
-      <c r="R18">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>day</t>
   </si>
@@ -85,7 +85,7 @@
     <t>09_01</t>
   </si>
   <si>
-    <t>start0_1</t>
+    <t>doWork1_1</t>
   </si>
   <si>
     <t>day9_2</t>
@@ -139,9 +139,6 @@
     <t>day9_9</t>
   </si>
   <si>
-    <t>special1_2</t>
-  </si>
-  <si>
     <t>09_09</t>
   </si>
   <si>
@@ -169,13 +166,10 @@
     <t>doWork3_1</t>
   </si>
   <si>
-    <t>day9_12</t>
-  </si>
-  <si>
-    <t>special1_3</t>
-  </si>
-  <si>
-    <t>09_12</t>
+    <t>day9_14</t>
+  </si>
+  <si>
+    <t>09_14</t>
   </si>
   <si>
     <t>doWork3_2</t>
@@ -404,7 +398,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,6 +408,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,7 +736,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -760,16 +760,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -778,93 +778,96 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1372,7 +1375,6 @@
       <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="K4"/>
       <c r="M4">
         <v>20</v>
       </c>
@@ -1523,9 +1525,7 @@
       <c r="J7" t="s">
         <v>35</v>
       </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
+      <c r="K7"/>
       <c r="M7">
         <v>80</v>
       </c>
@@ -1549,13 +1549,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" t="s">
         <v>39</v>
-      </c>
-      <c r="L8" t="s">
-        <v>40</v>
       </c>
       <c r="M8">
         <v>80</v>
@@ -1601,13 +1601,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M9">
         <v>120</v>
@@ -1645,54 +1645,52 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
-      <c r="A10">
+    <row r="10" s="1" customFormat="1" spans="1:17">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E10">
-        <v>0.4</v>
-      </c>
-      <c r="F10">
-        <v>0.4</v>
-      </c>
-      <c r="G10">
-        <v>0.2</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10">
+      <c r="K10" s="1"/>
+      <c r="M10" s="1">
         <v>120</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>160</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>120</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
@@ -1702,13 +1700,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11">
         <v>0.4</v>
@@ -1726,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M11">
         <v>120</v>
@@ -1746,54 +1744,54 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:17">
-      <c r="A12" s="1">
+    <row r="12" s="2" customFormat="1" spans="1:17">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2">
+        <v>200</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1">
-        <v>200</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H12" s="1">
-        <v>4</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="1">
+      <c r="M12" s="2">
         <v>120</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>160</v>
       </c>
-      <c r="O12" s="1">
+      <c r="O12" s="2">
         <v>120</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
@@ -1803,13 +1801,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1827,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M13">
         <v>120</v>
@@ -1855,7 +1853,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -1879,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M14">
         <v>28</v>
@@ -1903,7 +1901,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -1927,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M15">
         <v>29</v>
@@ -1951,7 +1949,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -1975,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M16">
         <v>30</v>
@@ -2002,7 +2000,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -2026,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M17">
         <v>31</v>
@@ -2050,7 +2048,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -2074,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M18">
         <v>32</v>

--- a/day.xlsx
+++ b/day.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>day</t>
   </si>
@@ -148,9 +148,6 @@
     <t>day9_10</t>
   </si>
   <si>
-    <t>failed1_2</t>
-  </si>
-  <si>
     <t>09_10</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
   </si>
   <si>
     <t>day9_16</t>
-  </si>
-  <si>
-    <t>failed1_3</t>
   </si>
   <si>
     <t>09_16</t>
@@ -1525,7 +1519,6 @@
       <c r="J7" t="s">
         <v>35</v>
       </c>
-      <c r="K7"/>
       <c r="M7">
         <v>80</v>
       </c>
@@ -1576,7 +1569,7 @@
         <v>38</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M8">
         <v>80</v>
@@ -1601,13 +1594,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1625,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M9">
         <v>120</v>
@@ -1650,13 +1643,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1">
         <v>100</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1">
         <v>0.4</v>
@@ -1674,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K10" s="1"/>
       <c r="M10" s="1">
@@ -1700,13 +1693,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11">
         <v>0.4</v>
@@ -1724,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M11">
         <v>120</v>
@@ -1749,13 +1742,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2">
         <v>200</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2">
         <v>0.4</v>
@@ -1773,10 +1766,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="M12" s="2">
         <v>120</v>
@@ -1801,13 +1794,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -1825,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M13">
         <v>120</v>
@@ -1853,7 +1846,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -1877,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M14">
         <v>28</v>
@@ -1901,7 +1894,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -1925,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M15">
         <v>29</v>
@@ -1949,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -1973,10 +1966,10 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M16">
         <v>30</v>
@@ -2000,7 +1993,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -2024,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M17">
         <v>31</v>
@@ -2048,7 +2041,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -2072,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M18">
         <v>32</v>
